--- a/informes_data/Euroleague/2025-26/Regular_Season/individual/NP_play_by_play_EL_101_R11.xlsx
+++ b/informes_data/Euroleague/2025-26/Regular_Season/individual/NP_play_by_play_EL_101_R11.xlsx
@@ -565,13 +565,13 @@
         <v>1</v>
       </c>
       <c r="D2" t="n">
-        <v>5.3452</v>
+        <v>6.1076</v>
       </c>
       <c r="E2" t="n">
-        <v>4.7617</v>
+        <v>5.2216</v>
       </c>
       <c r="F2" t="n">
-        <v>0.5835</v>
+        <v>0.8859</v>
       </c>
       <c r="G2" t="n">
         <v>1.0369</v>
@@ -610,13 +610,13 @@
         <v>2.3195</v>
       </c>
       <c r="S2" t="n">
-        <v>-0.0655</v>
+        <v>0.6969</v>
       </c>
       <c r="T2" t="n">
-        <v>0.7591</v>
+        <v>1.219</v>
       </c>
       <c r="U2" t="n">
-        <v>-0.8246</v>
+        <v>-0.5221</v>
       </c>
       <c r="V2" t="n">
         <v>2.2862</v>
@@ -631,7 +631,7 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>N. MELLI</t>
+          <t>O. BITIM</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
@@ -643,58 +643,58 @@
         <v>1</v>
       </c>
       <c r="D3" t="n">
-        <v>4.5056</v>
+        <v>4.0536</v>
       </c>
       <c r="E3" t="n">
-        <v>1.0147</v>
+        <v>1.6685</v>
       </c>
       <c r="F3" t="n">
-        <v>3.4908</v>
+        <v>2.3851</v>
       </c>
       <c r="G3" t="n">
-        <v>-0.08989999999999999</v>
+        <v>3.1229</v>
       </c>
       <c r="H3" t="n">
-        <v>-0.2606</v>
+        <v>2.4202</v>
       </c>
       <c r="I3" t="n">
-        <v>0.1707</v>
+        <v>0.7027</v>
       </c>
       <c r="J3" t="n">
-        <v>-0.7117</v>
+        <v>1.7862</v>
       </c>
       <c r="K3" t="n">
-        <v>-0.6246</v>
+        <v>1.3948</v>
       </c>
       <c r="L3" t="n">
-        <v>-0.0871</v>
+        <v>0.3914</v>
       </c>
       <c r="M3" t="n">
-        <v>0.6218</v>
+        <v>1.3367</v>
       </c>
       <c r="N3" t="n">
-        <v>0.364</v>
+        <v>1.0254</v>
       </c>
       <c r="O3" t="n">
-        <v>0.2578</v>
+        <v>0.3113</v>
       </c>
       <c r="P3" t="n">
         <v>0.9278</v>
       </c>
       <c r="Q3" t="n">
-        <v>-1.3917</v>
+        <v>0</v>
       </c>
       <c r="R3" t="n">
-        <v>2.3195</v>
+        <v>0.9278</v>
       </c>
       <c r="S3" t="n">
-        <v>3.6677</v>
+        <v>0.0029</v>
       </c>
       <c r="T3" t="n">
-        <v>3.1181</v>
+        <v>-0.1177</v>
       </c>
       <c r="U3" t="n">
-        <v>0.5496</v>
+        <v>0.1206</v>
       </c>
       <c r="V3" t="n">
         <v>0</v>
@@ -709,7 +709,7 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>O. BITIM</t>
+          <t>N. MELLI</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
@@ -721,58 +721,58 @@
         <v>1</v>
       </c>
       <c r="D4" t="n">
-        <v>3.466</v>
+        <v>2.6414</v>
       </c>
       <c r="E4" t="n">
-        <v>1.0473</v>
+        <v>-0.4125</v>
       </c>
       <c r="F4" t="n">
-        <v>2.4187</v>
+        <v>3.054</v>
       </c>
       <c r="G4" t="n">
-        <v>3.1229</v>
+        <v>-0.08989999999999999</v>
       </c>
       <c r="H4" t="n">
-        <v>2.4202</v>
+        <v>-0.2606</v>
       </c>
       <c r="I4" t="n">
-        <v>0.7027</v>
+        <v>0.1707</v>
       </c>
       <c r="J4" t="n">
-        <v>1.7862</v>
+        <v>-0.7117</v>
       </c>
       <c r="K4" t="n">
-        <v>1.3948</v>
+        <v>-0.6246</v>
       </c>
       <c r="L4" t="n">
-        <v>0.3914</v>
+        <v>-0.0871</v>
       </c>
       <c r="M4" t="n">
-        <v>1.3367</v>
+        <v>0.6218</v>
       </c>
       <c r="N4" t="n">
-        <v>1.0254</v>
+        <v>0.364</v>
       </c>
       <c r="O4" t="n">
-        <v>0.3113</v>
+        <v>0.2578</v>
       </c>
       <c r="P4" t="n">
         <v>0.9278</v>
       </c>
       <c r="Q4" t="n">
-        <v>0</v>
+        <v>-1.3917</v>
       </c>
       <c r="R4" t="n">
-        <v>0.9278</v>
+        <v>2.3195</v>
       </c>
       <c r="S4" t="n">
-        <v>-0.5847</v>
+        <v>1.8035</v>
       </c>
       <c r="T4" t="n">
-        <v>-0.7389</v>
+        <v>1.6909</v>
       </c>
       <c r="U4" t="n">
-        <v>0.1542</v>
+        <v>0.1127</v>
       </c>
       <c r="V4" t="n">
         <v>0</v>
@@ -799,10 +799,10 @@
         <v>1</v>
       </c>
       <c r="D5" t="n">
-        <v>1.5181</v>
+        <v>2.4931</v>
       </c>
       <c r="E5" t="n">
-        <v>2.5658</v>
+        <v>3.5408</v>
       </c>
       <c r="F5" t="n">
         <v>-1.0477</v>
@@ -844,10 +844,10 @@
         <v>2.0876</v>
       </c>
       <c r="S5" t="n">
-        <v>-0</v>
+        <v>0.975</v>
       </c>
       <c r="T5" t="n">
-        <v>-0.0351</v>
+        <v>0.9399</v>
       </c>
       <c r="U5" t="n">
         <v>0.0351</v>
@@ -865,7 +865,7 @@
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>A. BACOT JR.</t>
+          <t>B. COLSON</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
@@ -877,73 +877,73 @@
         <v>1</v>
       </c>
       <c r="D6" t="n">
-        <v>1.4647</v>
+        <v>1.2332</v>
       </c>
       <c r="E6" t="n">
-        <v>1.4232</v>
+        <v>-0.7516</v>
       </c>
       <c r="F6" t="n">
-        <v>0.0415</v>
+        <v>1.9848</v>
       </c>
       <c r="G6" t="n">
-        <v>0.7796999999999999</v>
+        <v>-0.4374</v>
       </c>
       <c r="H6" t="n">
-        <v>0.6291</v>
+        <v>-1.9665</v>
       </c>
       <c r="I6" t="n">
-        <v>0.1506</v>
+        <v>1.5291</v>
       </c>
       <c r="J6" t="n">
-        <v>0.6796</v>
+        <v>-0.9877</v>
       </c>
       <c r="K6" t="n">
-        <v>0.0539</v>
+        <v>-2.5201</v>
       </c>
       <c r="L6" t="n">
-        <v>0.6257</v>
+        <v>1.5324</v>
       </c>
       <c r="M6" t="n">
-        <v>0.1001</v>
+        <v>0.5503</v>
       </c>
       <c r="N6" t="n">
-        <v>0.5752</v>
+        <v>0.5536</v>
       </c>
       <c r="O6" t="n">
-        <v>-0.4751</v>
+        <v>-0.0033</v>
       </c>
       <c r="P6" t="n">
-        <v>-0.6959</v>
+        <v>0.9278</v>
       </c>
       <c r="Q6" t="n">
-        <v>-1.1598</v>
+        <v>-0.232</v>
       </c>
       <c r="R6" t="n">
-        <v>0.4639</v>
+        <v>1.1598</v>
       </c>
       <c r="S6" t="n">
-        <v>1.7752</v>
+        <v>0.8845</v>
       </c>
       <c r="T6" t="n">
-        <v>1.7616</v>
+        <v>0.4681</v>
       </c>
       <c r="U6" t="n">
-        <v>0.0136</v>
+        <v>0.4165</v>
       </c>
       <c r="V6" t="n">
-        <v>-0.3943</v>
+        <v>-0.1418</v>
       </c>
       <c r="W6" t="n">
-        <v>0.1418</v>
+        <v>0</v>
       </c>
       <c r="X6" t="n">
-        <v>-0.5361</v>
+        <v>-0.1418</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>B. COLSON</t>
+          <t>A. BACOT JR.</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
@@ -955,67 +955,67 @@
         <v>1</v>
       </c>
       <c r="D7" t="n">
-        <v>1.0735</v>
+        <v>0.292</v>
       </c>
       <c r="E7" t="n">
-        <v>-1.1802</v>
+        <v>0.0825</v>
       </c>
       <c r="F7" t="n">
-        <v>2.2536</v>
+        <v>0.2096</v>
       </c>
       <c r="G7" t="n">
-        <v>-0.4374</v>
+        <v>0.7796999999999999</v>
       </c>
       <c r="H7" t="n">
-        <v>-1.9665</v>
+        <v>0.6291</v>
       </c>
       <c r="I7" t="n">
-        <v>1.5291</v>
+        <v>0.1506</v>
       </c>
       <c r="J7" t="n">
-        <v>-0.9877</v>
+        <v>0.6796</v>
       </c>
       <c r="K7" t="n">
-        <v>-2.5201</v>
+        <v>0.0539</v>
       </c>
       <c r="L7" t="n">
-        <v>1.5324</v>
+        <v>0.6257</v>
       </c>
       <c r="M7" t="n">
-        <v>0.5503</v>
+        <v>0.1001</v>
       </c>
       <c r="N7" t="n">
-        <v>0.5536</v>
+        <v>0.5752</v>
       </c>
       <c r="O7" t="n">
-        <v>-0.0033</v>
+        <v>-0.4751</v>
       </c>
       <c r="P7" t="n">
-        <v>0.9278</v>
+        <v>-0.6959</v>
       </c>
       <c r="Q7" t="n">
-        <v>-0.232</v>
+        <v>-1.1598</v>
       </c>
       <c r="R7" t="n">
-        <v>1.1598</v>
+        <v>0.4639</v>
       </c>
       <c r="S7" t="n">
-        <v>0.7248</v>
+        <v>0.6025</v>
       </c>
       <c r="T7" t="n">
-        <v>0.0395</v>
+        <v>0.4208</v>
       </c>
       <c r="U7" t="n">
-        <v>0.6853</v>
+        <v>0.1817</v>
       </c>
       <c r="V7" t="n">
-        <v>-0.1418</v>
+        <v>-0.3943</v>
       </c>
       <c r="W7" t="n">
-        <v>0</v>
+        <v>0.1418</v>
       </c>
       <c r="X7" t="n">
-        <v>-0.1418</v>
+        <v>-0.5361</v>
       </c>
     </row>
     <row r="8">
@@ -1033,13 +1033,13 @@
         <v>1</v>
       </c>
       <c r="D8" t="n">
-        <v>1.011</v>
+        <v>0.2264</v>
       </c>
       <c r="E8" t="n">
-        <v>-0.3206</v>
+        <v>-1.0716</v>
       </c>
       <c r="F8" t="n">
-        <v>1.3315</v>
+        <v>1.2979</v>
       </c>
       <c r="G8" t="n">
         <v>-1.3845</v>
@@ -1078,13 +1078,13 @@
         <v>1.1598</v>
       </c>
       <c r="S8" t="n">
-        <v>1.2357</v>
+        <v>0.4512</v>
       </c>
       <c r="T8" t="n">
-        <v>1.1246</v>
+        <v>0.3736</v>
       </c>
       <c r="U8" t="n">
-        <v>0.1111</v>
+        <v>0.0775</v>
       </c>
       <c r="V8" t="n">
         <v>0</v>
@@ -1111,13 +1111,13 @@
         <v>1</v>
       </c>
       <c r="D9" t="n">
-        <v>-1.039</v>
+        <v>-0.6111</v>
       </c>
       <c r="E9" t="n">
-        <v>-2.2859</v>
+        <v>-2.0933</v>
       </c>
       <c r="F9" t="n">
-        <v>1.2469</v>
+        <v>1.4822</v>
       </c>
       <c r="G9" t="n">
         <v>0.4946</v>
@@ -1156,13 +1156,13 @@
         <v>0</v>
       </c>
       <c r="S9" t="n">
-        <v>-0.3738</v>
+        <v>0.054</v>
       </c>
       <c r="T9" t="n">
-        <v>-0.3734</v>
+        <v>-0.1808</v>
       </c>
       <c r="U9" t="n">
-        <v>-0.0004</v>
+        <v>0.2348</v>
       </c>
       <c r="V9" t="n">
         <v>0</v>
@@ -1189,13 +1189,13 @@
         <v>1</v>
       </c>
       <c r="D10" t="n">
-        <v>-1.4309</v>
+        <v>-1.1368</v>
       </c>
       <c r="E10" t="n">
-        <v>-0.2068</v>
+        <v>0.2218</v>
       </c>
       <c r="F10" t="n">
-        <v>-1.2241</v>
+        <v>-1.3585</v>
       </c>
       <c r="G10" t="n">
         <v>-0.8591</v>
@@ -1234,13 +1234,13 @@
         <v>0.6959</v>
       </c>
       <c r="S10" t="n">
-        <v>-0.644</v>
+        <v>-0.3499</v>
       </c>
       <c r="T10" t="n">
-        <v>-0.6721</v>
+        <v>-0.2436</v>
       </c>
       <c r="U10" t="n">
-        <v>0.0281</v>
+        <v>-0.1063</v>
       </c>
       <c r="V10" t="n">
         <v>0.5361</v>
@@ -1267,13 +1267,13 @@
         <v>1</v>
       </c>
       <c r="D11" t="n">
-        <v>-3.7692</v>
+        <v>-2.3759</v>
       </c>
       <c r="E11" t="n">
-        <v>-5.3858</v>
+        <v>-4.2615</v>
       </c>
       <c r="F11" t="n">
-        <v>1.6167</v>
+        <v>1.8855</v>
       </c>
       <c r="G11" t="n">
         <v>-0.9513</v>
@@ -1312,13 +1312,13 @@
         <v>1.6237</v>
       </c>
       <c r="S11" t="n">
-        <v>-0.1942</v>
+        <v>1.1991</v>
       </c>
       <c r="T11" t="n">
-        <v>-0.1766</v>
+        <v>0.9478</v>
       </c>
       <c r="U11" t="n">
-        <v>-0.0176</v>
+        <v>0.2513</v>
       </c>
       <c r="V11" t="n">
         <v>-0.5361</v>
@@ -1345,13 +1345,13 @@
         <v>1</v>
       </c>
       <c r="D12" t="n">
-        <v>-4.9111</v>
+        <v>-4.1959</v>
       </c>
       <c r="E12" t="n">
-        <v>-3.6592</v>
+        <v>-2.8768</v>
       </c>
       <c r="F12" t="n">
-        <v>-1.2519</v>
+        <v>-1.3191</v>
       </c>
       <c r="G12" t="n">
         <v>-1.6932</v>
@@ -1390,13 +1390,13 @@
         <v>1.1598</v>
       </c>
       <c r="S12" t="n">
-        <v>-0.4498</v>
+        <v>0.2653</v>
       </c>
       <c r="T12" t="n">
-        <v>-0.4402</v>
+        <v>0.3422</v>
       </c>
       <c r="U12" t="n">
-        <v>-0.0097</v>
+        <v>-0.0769</v>
       </c>
       <c r="V12" t="n">
         <v>-1.6083</v>
@@ -1423,22 +1423,22 @@
         <v>1</v>
       </c>
       <c r="D13" t="n">
-        <v>7.233899999999999</v>
+        <v>8.727599999999999</v>
       </c>
       <c r="E13" t="n">
-        <v>-2.225799999999999</v>
+        <v>-0.7321000000000004</v>
       </c>
       <c r="F13" t="n">
-        <v>9.459499999999998</v>
+        <v>9.4597</v>
       </c>
       <c r="G13" t="n">
-        <v>2.253200000000001</v>
+        <v>2.2532</v>
       </c>
       <c r="H13" t="n">
-        <v>1.7345</v>
+        <v>1.734499999999999</v>
       </c>
       <c r="I13" t="n">
-        <v>0.5188000000000004</v>
+        <v>0.5187999999999999</v>
       </c>
       <c r="J13" t="n">
         <v>3.0049</v>
@@ -1468,13 +1468,13 @@
         <v>13.9173</v>
       </c>
       <c r="S13" t="n">
-        <v>5.0914</v>
+        <v>6.584999999999999</v>
       </c>
       <c r="T13" t="n">
-        <v>4.3666</v>
+        <v>5.860200000000001</v>
       </c>
       <c r="U13" t="n">
-        <v>0.7247</v>
+        <v>0.7249000000000001</v>
       </c>
       <c r="V13" t="n">
         <v>-0.1107</v>
@@ -1501,13 +1501,13 @@
         <v>1</v>
       </c>
       <c r="D14" t="n">
-        <v>2.0564</v>
+        <v>2.3151</v>
       </c>
       <c r="E14" t="n">
-        <v>1.1937</v>
+        <v>1.4296</v>
       </c>
       <c r="F14" t="n">
-        <v>0.8626</v>
+        <v>0.8855</v>
       </c>
       <c r="G14" t="n">
         <v>0.9714</v>
@@ -1546,13 +1546,13 @@
         <v>2.0876</v>
       </c>
       <c r="S14" t="n">
-        <v>-0.8997000000000001</v>
+        <v>-0.6409</v>
       </c>
       <c r="T14" t="n">
-        <v>-0.2434</v>
+        <v>-0.0075</v>
       </c>
       <c r="U14" t="n">
-        <v>-0.6563</v>
+        <v>-0.6335</v>
       </c>
       <c r="V14" t="n">
         <v>2.6805</v>
@@ -1579,13 +1579,13 @@
         <v>1</v>
       </c>
       <c r="D15" t="n">
-        <v>1.3214</v>
+        <v>2.0685</v>
       </c>
       <c r="E15" t="n">
-        <v>-0.5719</v>
+        <v>0.0179</v>
       </c>
       <c r="F15" t="n">
-        <v>1.8933</v>
+        <v>2.0506</v>
       </c>
       <c r="G15" t="n">
         <v>0.773</v>
@@ -1624,13 +1624,13 @@
         <v>1.8556</v>
       </c>
       <c r="S15" t="n">
-        <v>-1.954</v>
+        <v>-1.207</v>
       </c>
       <c r="T15" t="n">
-        <v>-1.1202</v>
+        <v>-0.5305</v>
       </c>
       <c r="U15" t="n">
-        <v>-0.8338</v>
+        <v>-0.6765</v>
       </c>
       <c r="V15" t="n">
         <v>0.6468</v>
@@ -1645,7 +1645,7 @@
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>D. OTURU</t>
+          <t>G. PALATIN</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
@@ -1657,58 +1657,58 @@
         <v>1</v>
       </c>
       <c r="D16" t="n">
-        <v>1.055</v>
+        <v>0.1023</v>
       </c>
       <c r="E16" t="n">
-        <v>1.0982</v>
+        <v>0.1612</v>
       </c>
       <c r="F16" t="n">
-        <v>-0.0432</v>
+        <v>-0.0589</v>
       </c>
       <c r="G16" t="n">
-        <v>-1.0119</v>
+        <v>-0.0323</v>
       </c>
       <c r="H16" t="n">
-        <v>-0.3662</v>
+        <v>-0.1896</v>
       </c>
       <c r="I16" t="n">
-        <v>-0.6457000000000001</v>
+        <v>0.1573</v>
       </c>
       <c r="J16" t="n">
-        <v>0.2249</v>
+        <v>0</v>
       </c>
       <c r="K16" t="n">
-        <v>0.07770000000000001</v>
+        <v>0</v>
       </c>
       <c r="L16" t="n">
-        <v>0.1472</v>
+        <v>0</v>
       </c>
       <c r="M16" t="n">
-        <v>-1.2368</v>
+        <v>-0.0323</v>
       </c>
       <c r="N16" t="n">
-        <v>-0.4439</v>
+        <v>-0.1896</v>
       </c>
       <c r="O16" t="n">
-        <v>-0.7929</v>
+        <v>0.1573</v>
       </c>
       <c r="P16" t="n">
-        <v>-1.8556</v>
+        <v>0.232</v>
       </c>
       <c r="Q16" t="n">
-        <v>-2.5515</v>
+        <v>0</v>
       </c>
       <c r="R16" t="n">
-        <v>0.6959</v>
+        <v>0.232</v>
       </c>
       <c r="S16" t="n">
-        <v>3.9225</v>
+        <v>-0.0973</v>
       </c>
       <c r="T16" t="n">
-        <v>3.4248</v>
+        <v>0.1612</v>
       </c>
       <c r="U16" t="n">
-        <v>0.4977</v>
+        <v>-0.2585</v>
       </c>
       <c r="V16" t="n">
         <v>0</v>
@@ -1723,7 +1723,7 @@
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>G. PALATIN</t>
+          <t>A. BLAKENEY</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
@@ -1735,64 +1735,64 @@
         <v>1</v>
       </c>
       <c r="D17" t="n">
-        <v>-0.1672</v>
+        <v>-0.3031</v>
       </c>
       <c r="E17" t="n">
-        <v>-0.0747</v>
+        <v>-0.4989</v>
       </c>
       <c r="F17" t="n">
-        <v>-0.0925</v>
+        <v>0.1959</v>
       </c>
       <c r="G17" t="n">
-        <v>-0.0323</v>
+        <v>-1.4429</v>
       </c>
       <c r="H17" t="n">
-        <v>-0.1896</v>
+        <v>1.8463</v>
       </c>
       <c r="I17" t="n">
-        <v>0.1573</v>
+        <v>-3.2892</v>
       </c>
       <c r="J17" t="n">
-        <v>0</v>
+        <v>-0.7957</v>
       </c>
       <c r="K17" t="n">
-        <v>0</v>
+        <v>1.6504</v>
       </c>
       <c r="L17" t="n">
-        <v>0</v>
+        <v>-2.4461</v>
       </c>
       <c r="M17" t="n">
-        <v>-0.0323</v>
+        <v>-0.6472</v>
       </c>
       <c r="N17" t="n">
-        <v>-0.1896</v>
+        <v>0.196</v>
       </c>
       <c r="O17" t="n">
-        <v>0.1573</v>
+        <v>-0.8431</v>
       </c>
       <c r="P17" t="n">
-        <v>0.232</v>
+        <v>1.6237</v>
       </c>
       <c r="Q17" t="n">
         <v>0</v>
       </c>
       <c r="R17" t="n">
-        <v>0.232</v>
+        <v>1.6237</v>
       </c>
       <c r="S17" t="n">
-        <v>-0.3668</v>
+        <v>-1.1617</v>
       </c>
       <c r="T17" t="n">
-        <v>-0.0747</v>
+        <v>-0.3811</v>
       </c>
       <c r="U17" t="n">
-        <v>-0.2921</v>
+        <v>-0.7806</v>
       </c>
       <c r="V17" t="n">
-        <v>0</v>
+        <v>0.6778999999999999</v>
       </c>
       <c r="W17" t="n">
-        <v>0</v>
+        <v>0.6778999999999999</v>
       </c>
       <c r="X17" t="n">
         <v>0</v>
@@ -1801,7 +1801,7 @@
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>T. ODIASE</t>
+          <t>C. JONES</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
@@ -1813,58 +1813,58 @@
         <v>1</v>
       </c>
       <c r="D18" t="n">
-        <v>-0.4731</v>
+        <v>-0.7009</v>
       </c>
       <c r="E18" t="n">
-        <v>-1.2387</v>
+        <v>-1.4329</v>
       </c>
       <c r="F18" t="n">
-        <v>0.7655999999999999</v>
+        <v>0.7319</v>
       </c>
       <c r="G18" t="n">
-        <v>-0.7483</v>
+        <v>0.0519</v>
       </c>
       <c r="H18" t="n">
-        <v>-1.0996</v>
+        <v>0.07199999999999999</v>
       </c>
       <c r="I18" t="n">
-        <v>0.3513</v>
+        <v>-0.0201</v>
       </c>
       <c r="J18" t="n">
-        <v>-1.5023</v>
+        <v>-0.5839</v>
       </c>
       <c r="K18" t="n">
-        <v>-1.5391</v>
+        <v>-0.4601</v>
       </c>
       <c r="L18" t="n">
-        <v>0.0368</v>
+        <v>-0.1239</v>
       </c>
       <c r="M18" t="n">
-        <v>0.754</v>
+        <v>0.6358</v>
       </c>
       <c r="N18" t="n">
-        <v>0.4395</v>
+        <v>0.5321</v>
       </c>
       <c r="O18" t="n">
-        <v>0.3145</v>
+        <v>0.1038</v>
       </c>
       <c r="P18" t="n">
-        <v>0.9278</v>
+        <v>1.6237</v>
       </c>
       <c r="Q18" t="n">
-        <v>0</v>
+        <v>-0.232</v>
       </c>
       <c r="R18" t="n">
-        <v>0.9278</v>
+        <v>1.8556</v>
       </c>
       <c r="S18" t="n">
-        <v>0.4195</v>
+        <v>-1.3043</v>
       </c>
       <c r="T18" t="n">
-        <v>0.2636</v>
+        <v>-0.617</v>
       </c>
       <c r="U18" t="n">
-        <v>0.156</v>
+        <v>-0.6873</v>
       </c>
       <c r="V18" t="n">
         <v>-1.0722</v>
@@ -1879,7 +1879,7 @@
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>C. JONES</t>
+          <t>T. ODIASE</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
@@ -1891,58 +1891,58 @@
         <v>1</v>
       </c>
       <c r="D19" t="n">
-        <v>-1.1113</v>
+        <v>-0.9113</v>
       </c>
       <c r="E19" t="n">
-        <v>-1.7867</v>
+        <v>-1.7105</v>
       </c>
       <c r="F19" t="n">
-        <v>0.6755</v>
+        <v>0.7992</v>
       </c>
       <c r="G19" t="n">
-        <v>0.0519</v>
+        <v>-0.7483</v>
       </c>
       <c r="H19" t="n">
-        <v>0.07199999999999999</v>
+        <v>-1.0996</v>
       </c>
       <c r="I19" t="n">
-        <v>-0.0201</v>
+        <v>0.3513</v>
       </c>
       <c r="J19" t="n">
-        <v>-0.5839</v>
+        <v>-1.5023</v>
       </c>
       <c r="K19" t="n">
-        <v>-0.4601</v>
+        <v>-1.5391</v>
       </c>
       <c r="L19" t="n">
-        <v>-0.1239</v>
+        <v>0.0368</v>
       </c>
       <c r="M19" t="n">
-        <v>0.6358</v>
+        <v>0.754</v>
       </c>
       <c r="N19" t="n">
-        <v>0.5321</v>
+        <v>0.4395</v>
       </c>
       <c r="O19" t="n">
-        <v>0.1038</v>
+        <v>0.3145</v>
       </c>
       <c r="P19" t="n">
-        <v>1.6237</v>
+        <v>0.9278</v>
       </c>
       <c r="Q19" t="n">
-        <v>-0.232</v>
+        <v>0</v>
       </c>
       <c r="R19" t="n">
-        <v>1.8556</v>
+        <v>0.9278</v>
       </c>
       <c r="S19" t="n">
-        <v>-1.7146</v>
+        <v>-0.0187</v>
       </c>
       <c r="T19" t="n">
-        <v>-0.9709</v>
+        <v>-0.2082</v>
       </c>
       <c r="U19" t="n">
-        <v>-0.7437</v>
+        <v>0.1896</v>
       </c>
       <c r="V19" t="n">
         <v>-1.0722</v>
@@ -1957,7 +1957,7 @@
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>A. BLAKENEY</t>
+          <t>D. OTURU</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
@@ -1969,64 +1969,64 @@
         <v>1</v>
       </c>
       <c r="D20" t="n">
-        <v>-1.1173</v>
+        <v>-1.6065</v>
       </c>
       <c r="E20" t="n">
-        <v>-1.0887</v>
+        <v>-1.2608</v>
       </c>
       <c r="F20" t="n">
-        <v>-0.0286</v>
+        <v>-0.3457</v>
       </c>
       <c r="G20" t="n">
-        <v>-1.4429</v>
+        <v>-1.0119</v>
       </c>
       <c r="H20" t="n">
-        <v>1.8463</v>
+        <v>-0.3662</v>
       </c>
       <c r="I20" t="n">
-        <v>-3.2892</v>
+        <v>-0.6457000000000001</v>
       </c>
       <c r="J20" t="n">
-        <v>-0.7957</v>
+        <v>0.2249</v>
       </c>
       <c r="K20" t="n">
-        <v>1.6504</v>
+        <v>0.07770000000000001</v>
       </c>
       <c r="L20" t="n">
-        <v>-2.4461</v>
+        <v>0.1472</v>
       </c>
       <c r="M20" t="n">
-        <v>-0.6472</v>
+        <v>-1.2368</v>
       </c>
       <c r="N20" t="n">
-        <v>0.196</v>
+        <v>-0.4439</v>
       </c>
       <c r="O20" t="n">
-        <v>-0.8431</v>
+        <v>-0.7929</v>
       </c>
       <c r="P20" t="n">
-        <v>1.6237</v>
+        <v>-1.8556</v>
       </c>
       <c r="Q20" t="n">
-        <v>0</v>
+        <v>-2.5515</v>
       </c>
       <c r="R20" t="n">
-        <v>1.6237</v>
+        <v>0.6959</v>
       </c>
       <c r="S20" t="n">
-        <v>-1.976</v>
+        <v>1.261</v>
       </c>
       <c r="T20" t="n">
-        <v>-0.9709</v>
+        <v>1.0657</v>
       </c>
       <c r="U20" t="n">
-        <v>-1.0051</v>
+        <v>0.1953</v>
       </c>
       <c r="V20" t="n">
-        <v>0.6778999999999999</v>
+        <v>0</v>
       </c>
       <c r="W20" t="n">
-        <v>0.6778999999999999</v>
+        <v>0</v>
       </c>
       <c r="X20" t="n">
         <v>0</v>
@@ -2035,7 +2035,7 @@
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>J. MOTLEY</t>
+          <t>C. MALCOLM</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
@@ -2047,73 +2047,73 @@
         <v>1</v>
       </c>
       <c r="D21" t="n">
-        <v>-2.3248</v>
+        <v>-2.3163</v>
       </c>
       <c r="E21" t="n">
-        <v>-0.0862</v>
+        <v>-3.6687</v>
       </c>
       <c r="F21" t="n">
-        <v>-2.2386</v>
+        <v>1.3524</v>
       </c>
       <c r="G21" t="n">
-        <v>3.6876</v>
+        <v>-2.9392</v>
       </c>
       <c r="H21" t="n">
-        <v>2.821</v>
+        <v>0.1994</v>
       </c>
       <c r="I21" t="n">
-        <v>0.8666</v>
+        <v>-3.1386</v>
       </c>
       <c r="J21" t="n">
-        <v>4.5132</v>
+        <v>-2.753</v>
       </c>
       <c r="K21" t="n">
-        <v>2.9073</v>
+        <v>0.1715</v>
       </c>
       <c r="L21" t="n">
-        <v>1.606</v>
+        <v>-2.9246</v>
       </c>
       <c r="M21" t="n">
-        <v>-0.8256</v>
+        <v>-0.1861</v>
       </c>
       <c r="N21" t="n">
-        <v>-0.0862</v>
+        <v>0.0279</v>
       </c>
       <c r="O21" t="n">
-        <v>-0.7393999999999999</v>
+        <v>-0.214</v>
       </c>
       <c r="P21" t="n">
-        <v>-4.1751</v>
+        <v>1.6237</v>
       </c>
       <c r="Q21" t="n">
-        <v>-5.1029</v>
+        <v>-0.4639</v>
       </c>
       <c r="R21" t="n">
-        <v>0.9278</v>
+        <v>2.0876</v>
       </c>
       <c r="S21" t="n">
-        <v>0.3071</v>
+        <v>-0.859</v>
       </c>
       <c r="T21" t="n">
-        <v>0.5034</v>
+        <v>-0.4518</v>
       </c>
       <c r="U21" t="n">
-        <v>-0.1964</v>
+        <v>-0.4072</v>
       </c>
       <c r="V21" t="n">
-        <v>-2.1444</v>
+        <v>-0.1418</v>
       </c>
       <c r="W21" t="n">
         <v>0</v>
       </c>
       <c r="X21" t="n">
-        <v>-2.1444</v>
+        <v>-0.1418</v>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>C. MALCOLM</t>
+          <t>J. MOTLEY</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
@@ -2125,67 +2125,67 @@
         <v>1</v>
       </c>
       <c r="D22" t="n">
-        <v>-2.8947</v>
+        <v>-2.4599</v>
       </c>
       <c r="E22" t="n">
-        <v>-4.0226</v>
+        <v>-0.3221</v>
       </c>
       <c r="F22" t="n">
-        <v>1.1279</v>
+        <v>-2.1377</v>
       </c>
       <c r="G22" t="n">
-        <v>-2.9392</v>
+        <v>3.6876</v>
       </c>
       <c r="H22" t="n">
-        <v>0.1994</v>
+        <v>2.821</v>
       </c>
       <c r="I22" t="n">
-        <v>-3.1386</v>
+        <v>0.8666</v>
       </c>
       <c r="J22" t="n">
-        <v>-2.753</v>
+        <v>4.5132</v>
       </c>
       <c r="K22" t="n">
-        <v>0.1715</v>
+        <v>2.9073</v>
       </c>
       <c r="L22" t="n">
-        <v>-2.9246</v>
+        <v>1.606</v>
       </c>
       <c r="M22" t="n">
-        <v>-0.1861</v>
+        <v>-0.8256</v>
       </c>
       <c r="N22" t="n">
-        <v>0.0279</v>
+        <v>-0.0862</v>
       </c>
       <c r="O22" t="n">
-        <v>-0.214</v>
+        <v>-0.7393999999999999</v>
       </c>
       <c r="P22" t="n">
-        <v>1.6237</v>
+        <v>-4.1751</v>
       </c>
       <c r="Q22" t="n">
-        <v>-0.4639</v>
+        <v>-5.1029</v>
       </c>
       <c r="R22" t="n">
-        <v>2.0876</v>
+        <v>0.9278</v>
       </c>
       <c r="S22" t="n">
-        <v>-1.4374</v>
+        <v>0.172</v>
       </c>
       <c r="T22" t="n">
-        <v>-0.8057</v>
+        <v>0.2675</v>
       </c>
       <c r="U22" t="n">
-        <v>-0.6317</v>
+        <v>-0.0955</v>
       </c>
       <c r="V22" t="n">
-        <v>-0.1418</v>
+        <v>-2.1444</v>
       </c>
       <c r="W22" t="n">
         <v>0</v>
       </c>
       <c r="X22" t="n">
-        <v>-0.1418</v>
+        <v>-2.1444</v>
       </c>
     </row>
     <row r="23">
@@ -2203,13 +2203,13 @@
         <v>1</v>
       </c>
       <c r="D23" t="n">
-        <v>-3.5783</v>
+        <v>-2.6354</v>
       </c>
       <c r="E23" t="n">
-        <v>-3.4182</v>
+        <v>-2.7105</v>
       </c>
       <c r="F23" t="n">
-        <v>-0.1601</v>
+        <v>0.0751</v>
       </c>
       <c r="G23" t="n">
         <v>-1.5625</v>
@@ -2248,13 +2248,13 @@
         <v>1.6237</v>
       </c>
       <c r="S23" t="n">
-        <v>-1.3921</v>
+        <v>-0.4492</v>
       </c>
       <c r="T23" t="n">
-        <v>-0.731</v>
+        <v>-0.0233</v>
       </c>
       <c r="U23" t="n">
-        <v>-0.6611</v>
+        <v>-0.4259</v>
       </c>
       <c r="V23" t="n">
         <v>0.5361</v>
@@ -2281,16 +2281,16 @@
         <v>1</v>
       </c>
       <c r="D24" t="n">
-        <v>-7.233900000000001</v>
+        <v>-6.447500000000002</v>
       </c>
       <c r="E24" t="n">
-        <v>-9.995800000000001</v>
+        <v>-9.995700000000001</v>
       </c>
       <c r="F24" t="n">
-        <v>2.7619</v>
+        <v>3.5483</v>
       </c>
       <c r="G24" t="n">
-        <v>-2.2532</v>
+        <v>-2.253199999999999</v>
       </c>
       <c r="H24" t="n">
         <v>-1.734399999999999</v>
@@ -2317,7 +2317,7 @@
         <v>-3.4456</v>
       </c>
       <c r="P24" t="n">
-        <v>0.000100000000000211</v>
+        <v>9.99999999995449e-05</v>
       </c>
       <c r="Q24" t="n">
         <v>-13.9171</v>
@@ -2326,16 +2326,16 @@
         <v>13.9173</v>
       </c>
       <c r="S24" t="n">
-        <v>-5.0915</v>
+        <v>-4.305099999999999</v>
       </c>
       <c r="T24" t="n">
-        <v>-0.7250000000000003</v>
+        <v>-0.7249999999999998</v>
       </c>
       <c r="U24" t="n">
-        <v>-4.3665</v>
+        <v>-3.5801</v>
       </c>
       <c r="V24" t="n">
-        <v>0.1107000000000001</v>
+        <v>0.1107000000000002</v>
       </c>
       <c r="W24" t="n">
         <v>3.8945</v>
